--- a/BOM/Bill of Materials.xlsx
+++ b/BOM/Bill of Materials.xlsx
@@ -3988,7 +3988,9 @@
 </file>
 
 <file path=xl/revisions/userNames.xml><?xml version="1.0" encoding="utf-8"?>
-<users xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac" count="0"/>
+<users xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac" count="1">
+  <userInfo guid="{06866A0E-2521-4829-8C2E-AFD45F8E0E9C}" name="Chaitanya Gajbhiye" id="-1166906855" dateTime="2026-10-20T23:17:08"/>
+</users>
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
